--- a/artfynd/A 19417-2026 artfynd.xlsx
+++ b/artfynd/A 19417-2026 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115166471</v>
+        <v>115166469</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725386</v>
+        <v>725694</v>
       </c>
       <c r="R2" t="n">
-        <v>7212482</v>
+        <v>7212332</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115166469</v>
+        <v>115166471</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725694</v>
+        <v>725386</v>
       </c>
       <c r="R3" t="n">
-        <v>7212332</v>
+        <v>7212482</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
